--- a/output/laminas_comunales/comunal_s_isapre_a_2023_o_higgins.xlsx
+++ b/output/laminas_comunales/comunal_s_isapre_a_2023_o_higgins.xlsx
@@ -375,91 +375,91 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>6101</t>
+          <t>6108</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Rancagua</t>
+          <t>Machalí</t>
         </is>
       </c>
       <c r="C2">
-        <v>39572</v>
+        <v>34.30065499455659</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6108</t>
+          <t>6101</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Machalí</t>
+          <t>Rancagua</t>
         </is>
       </c>
       <c r="C3">
-        <v>19219</v>
+        <v>15.08303444490607</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>6111</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>San Fernando</t>
+          <t>Olivar</t>
         </is>
       </c>
       <c r="C4">
-        <v>8243</v>
+        <v>12.48842439476121</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6115</t>
+          <t>6116</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Rengo</t>
+          <t>Requínoa</t>
         </is>
       </c>
       <c r="C5">
-        <v>4172</v>
+        <v>11.80007626198926</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6116</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Requínoa</t>
+          <t>San Fernando</t>
         </is>
       </c>
       <c r="C6">
-        <v>4023</v>
+        <v>9.807841037539413</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6117</t>
+          <t>6103</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>San Vicente</t>
+          <t>Coinco</t>
         </is>
       </c>
       <c r="C7">
-        <v>3881</v>
+        <v>9.177798249654536</v>
       </c>
     </row>
     <row r="8">
@@ -474,397 +474,397 @@
         </is>
       </c>
       <c r="C8">
-        <v>3304</v>
+        <v>8.713769549278688</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6310</t>
+          <t>6105</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Santa Cruz</t>
+          <t>Doñihue</t>
         </is>
       </c>
       <c r="C9">
-        <v>3226</v>
+        <v>8.504700983127979</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6105</t>
+          <t>6102</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Doñihue</t>
+          <t>Codegua</t>
         </is>
       </c>
       <c r="C10">
-        <v>1981</v>
+        <v>8.072487644151565</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6110</t>
+          <t>6201</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mostazal</t>
+          <t>Pichilemu</t>
         </is>
       </c>
       <c r="C11">
-        <v>1944</v>
+        <v>7.709204579056309</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6111</t>
+          <t>6117</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Olivar</t>
+          <t>San Vicente</t>
         </is>
       </c>
       <c r="C12">
-        <v>1888</v>
+        <v>7.632551919446192</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6201</t>
+          <t>6205</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pichilemu</t>
+          <t>Navidad</t>
         </is>
       </c>
       <c r="C13">
-        <v>1825</v>
+        <v>7.359883791308558</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6303</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Chimbarongo</t>
+          <t>Santa Cruz</t>
         </is>
       </c>
       <c r="C14">
-        <v>1640</v>
+        <v>7.327654741624078</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6107</t>
+          <t>6110</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Las Cabras</t>
+          <t>Mostazal</t>
         </is>
       </c>
       <c r="C15">
-        <v>1538</v>
+        <v>6.871200339318535</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6104</t>
+          <t>6115</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Coltauco</t>
+          <t>Rengo</t>
         </is>
       </c>
       <c r="C16">
-        <v>1382</v>
+        <v>6.238971138029012</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6102</t>
+          <t>6202</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Codegua</t>
+          <t>La Estrella</t>
         </is>
       </c>
       <c r="C17">
-        <v>1274</v>
+        <v>6.194314806957998</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6305</t>
+          <t>6204</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nancagua</t>
+          <t>Marchigüe</t>
         </is>
       </c>
       <c r="C18">
-        <v>1114</v>
+        <v>5.885965810215989</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>6103</t>
+          <t>6308</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Coinco</t>
+          <t>Placilla</t>
         </is>
       </c>
       <c r="C19">
-        <v>797</v>
+        <v>5.87346553352219</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>6113</t>
+          <t>6104</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Pichidegua</t>
+          <t>Coltauco</t>
         </is>
       </c>
       <c r="C20">
-        <v>763</v>
+        <v>5.776625982277211</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>6114</t>
+          <t>6305</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Quinta de Tilcoco</t>
+          <t>Nancagua</t>
         </is>
       </c>
       <c r="C21">
-        <v>743</v>
+        <v>5.624274246478517</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>6112</t>
+          <t>6307</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Peumo</t>
+          <t>Peralillo</t>
         </is>
       </c>
       <c r="C22">
-        <v>731</v>
+        <v>5.442886966895317</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>6307</t>
+          <t>6203</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Peralillo</t>
+          <t>Litueche</t>
         </is>
       </c>
       <c r="C23">
-        <v>730</v>
+        <v>5.120289546519055</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>6109</t>
+          <t>6107</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Malloa</t>
+          <t>Las Cabras</t>
         </is>
       </c>
       <c r="C24">
-        <v>724</v>
+        <v>5.014835827708762</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>6114</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Placilla</t>
+          <t>Quinta de Tilcoco</t>
         </is>
       </c>
       <c r="C25">
-        <v>622</v>
+        <v>4.826242286456642</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>6205</t>
+          <t>6109</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Navidad</t>
+          <t>Malloa</t>
         </is>
       </c>
       <c r="C26">
-        <v>608</v>
+        <v>4.72800888134265</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>6302</t>
+          <t>6112</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Chépica</t>
+          <t>Peumo</t>
         </is>
       </c>
       <c r="C27">
-        <v>596</v>
+        <v>4.677202636125152</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>6204</t>
+          <t>6309</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Marchigüe</t>
+          <t>Pumanque</t>
         </is>
       </c>
       <c r="C28">
-        <v>575</v>
+        <v>4.320289527256277</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>6306</t>
+          <t>6303</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Palmilla</t>
+          <t>Chimbarongo</t>
         </is>
       </c>
       <c r="C29">
-        <v>483</v>
+        <v>4.119257528947831</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>6203</t>
+          <t>6304</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Litueche</t>
+          <t>Lolol</t>
         </is>
       </c>
       <c r="C30">
-        <v>481</v>
+        <v>3.986754966887417</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>6304</t>
+          <t>6306</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Lolol</t>
+          <t>Palmilla</t>
         </is>
       </c>
       <c r="C31">
-        <v>301</v>
+        <v>3.819087530639677</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>6202</t>
+          <t>6302</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>La Estrella</t>
+          <t>Chépica</t>
         </is>
       </c>
       <c r="C32">
-        <v>292</v>
+        <v>3.727096491776624</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>6206</t>
+          <t>6113</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Paredones</t>
+          <t>Pichidegua</t>
         </is>
       </c>
       <c r="C33">
-        <v>205</v>
+        <v>3.50466216526572</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>6309</t>
+          <t>6206</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Pumanque</t>
+          <t>Paredones</t>
         </is>
       </c>
       <c r="C34">
-        <v>191</v>
+        <v>2.904505525644658</v>
       </c>
     </row>
   </sheetData>
@@ -920,7 +920,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a ISAPRE</t>
+          <t>Porcentaje de residentes afiliados a ISAPRE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
